--- a/KatalonData/ABPTestDataDemo/PaymentsACH_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/PaymentsACH_Demo.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="226">
   <si>
     <t>Result</t>
   </si>
@@ -797,6 +797,219 @@
   </si>
   <si>
     <t>Fri Jul 24 17:52:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 22:55:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 22:55:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 22:55:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 22:56:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 22:56:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 22:57:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 22:57:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 22:58:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:02:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:03:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:07:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:08:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:08:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:09:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:09:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:10:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:11:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:11:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:12:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:57:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:58:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:58:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:58:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:59:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 07 23:59:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:00:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:00:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:01:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:05:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:06:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:07:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:08:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:09:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:10:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:11:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:12:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:13:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:14:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:15:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 00:16:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:12:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:12:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:13:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:14:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:15:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:16:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:17:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:18:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:22:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:23:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:24:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:25:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:26:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:27:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:31:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:32:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:33:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:34:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:34:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:35:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:36:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:37:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:01:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:01:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:01:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 13:59:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:01:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:04:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:05:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:07:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:08:56 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1470,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1336,10 +1549,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>53</v>
+        <v>194</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1440,10 +1653,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1566,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>11</v>
@@ -2332,7 +2545,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>123</v>
+        <v>225</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2637,7 +2850,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2737,7 +2950,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2840,7 +3053,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3071,7 +3284,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3222,7 +3435,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3372,7 +3585,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3402,7 +3615,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -3429,7 +3642,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -3502,7 +3715,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="12" t="s">
@@ -3598,7 +3811,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3744,7 +3957,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -3884,7 +4097,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4024,7 +4237,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4164,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4304,7 +4517,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4420,7 +4633,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4536,7 +4749,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4703,7 +4916,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>120</v>
+        <v>208</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4775,7 +4988,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>119</v>
+        <v>223</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4919,7 +5132,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>118</v>
+        <v>222</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4991,7 +5204,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
